--- a/data/아실_매교역팰루시드_전체매물_20261020.xlsx
+++ b/data/아실_매교역팰루시드_전체매물_20261020.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43344149</t>
+          <t>43391774</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -579,48 +579,48 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109,272</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -639,7 +639,11 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -650,14 +654,14 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O안전전세도이강O옵션가득한집,냉장고3,세탁기,인덕션등</t>
+          <t>O매매도이강O에어컨4대,인덕션,붙박이장,토허제</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>109272</v>
       </c>
       <c r="Z2" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -671,12 +675,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43355343</t>
+          <t>43391664</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -706,7 +710,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -717,17 +721,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108,402</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -737,7 +741,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -748,23 +752,23 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
+          <t>O매매도이강O피1.6억탑층,삼성물산,탁트인고층채광굿</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>108402</v>
       </c>
       <c r="Z3" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -783,7 +787,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43355345</t>
+          <t>43391326</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -793,27 +797,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -829,12 +833,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108,431</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -844,7 +848,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -859,27 +863,27 @@
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O전세대출가능O상시집보여드려요,당일확인,중문,에어컨4</t>
+          <t>O전세도이강O현금전세,메인동의조경뷰굿,에어컨4,붙박이장</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>108431</v>
       </c>
       <c r="Z4" t="n">
-        <v>45000</v>
+        <v>63000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -893,12 +897,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43355344</t>
+          <t>43391279</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -908,7 +912,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -928,7 +932,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -939,17 +943,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,030</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -959,7 +963,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -979,14 +983,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O매매도이강OP2.3억,귀한트인조망,채광환기굿</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>115030</v>
       </c>
       <c r="Z5" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1000,12 +1004,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43301888</t>
+          <t>43391132</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1015,27 +1019,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>121동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,17 +1060,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1086,21 +1090,25 @@
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O안전전세도이강O현금전세,빠른입주환영,에어컨4</t>
+          <t>O늦은입주OKO전입X,시에4,실링팬,중문,입주청소</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -1111,12 +1119,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43256614</t>
+          <t>43391080</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1126,7 +1134,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1157,17 +1165,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>108,431</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1177,7 +1185,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1186,10 +1194,18 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1197,14 +1213,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O전세도이강O거실넓은뻥뷰,영상참고하세요</t>
+          <t>O매매도이강OP1.6억,메인동의조경뷰굿,에어컨4,붙박이장</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>116830</v>
+        <v>108431</v>
       </c>
       <c r="Z7" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1218,12 +1234,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43252795</t>
+          <t>43389868</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1233,17 +1249,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>130동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1264,17 +1280,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91,000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1284,7 +1300,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1298,28 +1314,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
+          <t>O매매도이강O삼성사내대출가능,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="Z8" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1333,12 +1349,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>43252135</t>
+          <t>43388935</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1348,7 +1364,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1368,18 +1384,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1389,17 +1405,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1408,28 +1424,36 @@
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
+          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>10000</v>
+        <v>60000</v>
       </c>
       <c r="AA9" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1440,12 +1464,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43252123</t>
+          <t>43388930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1455,27 +1479,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1486,27 +1510,27 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119,720</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1522,25 +1546,25 @@
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,인덕션등</t>
+          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>119720</v>
       </c>
       <c r="Z10" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1556,7 +1580,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>43251927</t>
+          <t>43388921</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1566,22 +1590,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1602,7 +1626,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>114,530</t>
+          <t>119,372</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1617,7 +1641,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1626,11 +1650,7 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -1638,14 +1658,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
+          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>114530</v>
+        <v>119372</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1667,7 +1691,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>43251918</t>
+          <t>43388919</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1728,7 +1752,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1782,7 +1806,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43251902</t>
+          <t>43388064</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1792,27 +1816,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1833,7 +1857,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1843,7 +1867,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1852,13 +1876,17 @@
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>O</t>
@@ -1867,14 +1895,14 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>45000</v>
+        <v>47000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1893,7 +1921,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43210459</t>
+          <t>43388048</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1903,33 +1931,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>128동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1944,7 +1972,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1954,7 +1982,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1963,11 +1991,7 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>O</t>
@@ -1982,14 +2006,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O이강O빠른입주환영,현금전세,에어컨4,채광굿</t>
+          <t>O71타입로얄동O채광굿,입주협의가능</t>
         </is>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2003,12 +2027,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43165287</t>
+          <t>43388036</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2018,22 +2042,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2049,17 +2073,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>119,720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2069,7 +2093,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2083,24 +2107,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
+          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>119720</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2114,12 +2142,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43165270</t>
+          <t>43388023</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2129,7 +2157,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2149,7 +2177,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2160,17 +2188,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>115,030</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2180,7 +2208,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2190,24 +2218,24 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
+          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>115030</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2221,12 +2249,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>43199433</t>
+          <t>43388011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2256,7 +2284,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2267,7 +2295,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2277,17 +2305,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2302,11 +2330,7 @@
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>O</t>
@@ -2315,17 +2339,17 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
+          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,인덕션등</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
@@ -2336,12 +2360,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43164394</t>
+          <t>43388001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2351,27 +2375,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2382,17 +2406,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>115,272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2402,7 +2426,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2416,24 +2440,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
+          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>115272</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2452,7 +2480,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>43164195</t>
+          <t>43423016</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2462,27 +2490,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>117동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2503,7 +2531,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2513,7 +2541,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2522,7 +2550,11 @@
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
@@ -2537,14 +2569,14 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
+          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2558,12 +2590,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>43160256</t>
+          <t>43387061</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2573,27 +2605,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2604,27 +2636,27 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,272</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2633,36 +2665,32 @@
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O매매도이강O협의가능,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>115272</v>
       </c>
       <c r="Z20" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2678,7 +2706,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>43124662</t>
+          <t>43423017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2688,7 +2716,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2708,7 +2736,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2729,7 +2757,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2739,7 +2767,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2748,33 +2776,25 @@
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>60000</v>
+        <v>53000</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2793,7 +2813,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>43070764</t>
+          <t>43344149</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2803,27 +2823,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2844,7 +2864,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2854,7 +2874,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2865,27 +2885,23 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>O전세대출가능O와이드주방,채광좋아요,조용하고따뜻한동</t>
+          <t>O안전전세도이강O옵션가득한집,냉장고3,세탁기,인덕션등</t>
         </is>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>55000</v>
+        <v>45000</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -2899,12 +2915,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>43070716</t>
+          <t>43355343</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2914,7 +2930,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>107동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2934,7 +2950,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2945,7 +2961,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2955,17 +2971,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2975,31 +2991,27 @@
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>O전입가능O입주협의,융무,채광좋은집</t>
+          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
         </is>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>10000</v>
+        <v>55000</v>
       </c>
       <c r="AA23" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3010,12 +3022,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>43070693</t>
+          <t>43355345</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3025,27 +3037,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3056,17 +3068,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>119,372</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3076,7 +3088,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3085,29 +3097,33 @@
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
+          <t>O전세대출가능O상시집보여드려요,당일확인,중문,에어컨4</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>119372</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3121,12 +3137,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>42954753</t>
+          <t>43301888</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3136,27 +3152,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>121동</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3167,17 +3183,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3187,7 +3203,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3196,25 +3212,29 @@
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+          <t>O안전전세도이강O현금전세,빠른입주환영,에어컨4</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>89000</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3233,7 +3253,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>42952675</t>
+          <t>43256614</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3243,7 +3263,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3279,7 +3299,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3294,7 +3314,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3307,14 +3327,18 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>O조건맞춰찾아드립니다O전월세매물많은집</t>
+          <t>O전세도이강O거실넓은뻥뷰,영상참고하세요</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z26" t="n">
         <v>55000</v>
@@ -3336,7 +3360,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42952648</t>
+          <t>43252135</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3346,33 +3370,33 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3387,17 +3411,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3407,27 +3431,27 @@
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
+          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
         </is>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="AA27" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
@@ -3443,7 +3467,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>42952568</t>
+          <t>43251927</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3453,27 +3477,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3489,7 +3513,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>114,530</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3504,7 +3528,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3513,7 +3537,11 @@
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
@@ -3524,11 +3552,11 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>O조합원매물설명必O손님분들전화환영합니다</t>
+          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>92000</v>
+        <v>114530</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3545,12 +3573,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>42952559</t>
+          <t>43251902</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3560,22 +3588,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,7 +3619,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3601,17 +3629,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3626,30 +3654,26 @@
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="AA29" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3665,7 +3689,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42852176</t>
+          <t>43210459</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3675,27 +3699,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>125동</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3716,7 +3740,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3726,7 +3750,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3735,29 +3759,33 @@
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
+          <t>O이강O빠른입주환영,현금전세,에어컨4,채광굿</t>
         </is>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -3776,7 +3804,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>43164195</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3786,27 +3814,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3827,7 +3855,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3837,7 +3865,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3847,11 +3875,7 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>O</t>
@@ -3865,14 +3889,14 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
+          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
         </is>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>47000</v>
+        <v>60000</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -3886,12 +3910,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>42558979</t>
+          <t>43160256</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3901,38 +3925,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>128동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3942,17 +3966,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3962,13 +3986,17 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>O</t>
@@ -3976,17 +4004,17 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>O71타입로얄동O채광굿,입주협의가능</t>
+          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
@@ -4002,7 +4030,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42490328</t>
+          <t>43070764</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4012,7 +4040,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4032,7 +4060,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4053,7 +4081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4063,7 +4091,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4072,33 +4100,29 @@
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
+          <t>O전세대출가능O와이드주방,채광좋아요,조용하고따뜻한동</t>
         </is>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4112,12 +4136,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42441234</t>
+          <t>43070716</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4127,7 +4151,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>107동</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4147,7 +4171,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4158,7 +4182,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4168,17 +4192,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4195,19 +4219,570 @@
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
+          <t>O전입가능O입주협의,융무,채광좋은집</t>
         </is>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>42954753</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>129동</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>84.42</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>59.75</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>89,000</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>89000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>42952648</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>123동</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>101.02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>71.92</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>42952568</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>105동</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>84.32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>59.75</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>92,000</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>O조합원매물설명必O손님분들전화환영합니다</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>92000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>42952559</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>122동</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>101.34</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>71.89</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전세</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>42852176</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>101동</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>112.60</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>84.14</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>전세</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
         <v>60000</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AA39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4222,7 +4797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4375,7 +4950,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43251927</t>
+          <t>43391774</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4385,7 +4960,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4405,13 +4980,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -4421,7 +4996,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>114,530</t>
+          <t>109,272</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -4436,7 +5011,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4460,11 +5035,11 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
+          <t>O매매도이강O에어컨4대,인덕션,붙박이장,토허제</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>114530</v>
+        <v>109272</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -4486,7 +5061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43165287</t>
+          <t>43391664</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4496,27 +5071,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -4532,7 +5107,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>119,720</t>
+          <t>108,402</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4547,7 +5122,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -4556,11 +5131,7 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -4571,11 +5142,11 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
+          <t>O매매도이강O피1.6억탑층,삼성물산,탁트인고층채광굿</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>119720</v>
+        <v>108402</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -4597,7 +5168,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43165270</t>
+          <t>43391279</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4658,7 +5229,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -4678,7 +5249,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
+          <t>O매매도이강OP2.3억,귀한트인조망,채광환기굿</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -4704,7 +5275,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43164394</t>
+          <t>43391080</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4714,7 +5285,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4734,7 +5305,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -4750,7 +5321,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>115,272</t>
+          <t>108,431</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -4765,7 +5336,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4786,14 +5357,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
+          <t>O매매도이강OP1.6억,메인동의조경뷰굿,에어컨4,붙박이장</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>115272</v>
+        <v>108431</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -4815,7 +5390,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43070693</t>
+          <t>43389868</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4825,22 +5400,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>130동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4861,7 +5436,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>119,372</t>
+          <t>91,000</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -4876,7 +5451,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -4885,26 +5460,30 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
+          <t>O매매도이강O삼성사내대출가능,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>119372</v>
+        <v>91000</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -4926,7 +5505,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42954753</t>
+          <t>43388930</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4936,27 +5515,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -4972,7 +5551,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>119,720</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -4987,7 +5566,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4996,22 +5575,26 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>89000</v>
+        <v>119720</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -5033,7 +5616,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42952568</t>
+          <t>43388921</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5043,27 +5626,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -5079,7 +5662,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>119,372</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5094,7 +5677,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -5111,19 +5694,459 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>119372</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>43387061</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>109동</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>112.60</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>84.14</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>115,272</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>O매매도이강O협의가능,에어컨4,붙박이장,인덕션</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>115272</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>43251927</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>101동</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>112.60</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>84.14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>114,530</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>114530</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>42954753</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>129동</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>84.42</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>59.75</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>89,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>89000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>42952568</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>105동</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>84.32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>59.75</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>매매</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>92,000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>O조합원매물설명必O손님분들전화환영합니다</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y12" t="n">
         <v>92000</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5291,7 +6314,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43344149</t>
+          <t>43391326</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5301,27 +6324,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -5337,12 +6360,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108,431</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -5352,7 +6375,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5361,7 +6384,11 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -5369,17 +6396,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O안전전세도이강O옵션가득한집,냉장고3,세탁기,인덕션등</t>
+          <t>O전세도이강O현금전세,메인동의조경뷰굿,에어컨4,붙박이장</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>108431</v>
       </c>
       <c r="Z2" t="n">
-        <v>45000</v>
+        <v>63000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -5398,7 +6429,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43355343</t>
+          <t>43388935</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5408,7 +6439,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5428,7 +6459,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -5449,7 +6480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -5459,7 +6490,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -5468,8 +6499,16 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>O</t>
@@ -5479,14 +6518,14 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
+          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
         </is>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -5505,7 +6544,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43355345</t>
+          <t>43388919</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5515,27 +6554,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -5556,7 +6595,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -5566,7 +6605,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -5586,22 +6625,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O전세대출가능O상시집보여드려요,당일확인,중문,에어컨4</t>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -5620,7 +6659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43355344</t>
+          <t>43388064</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5630,27 +6669,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -5671,7 +6710,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -5681,7 +6720,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -5691,24 +6730,32 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
         </is>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>53000</v>
+        <v>47000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -5727,7 +6774,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43301888</t>
+          <t>43388048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5737,7 +6784,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>121동</t>
+          <t>128동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5757,13 +6804,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5778,7 +6825,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -5788,7 +6835,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -5797,11 +6844,7 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>O</t>
@@ -5809,17 +6852,21 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O안전전세도이강O현금전세,빠른입주환영,에어컨4</t>
+          <t>O71타입로얄동O채광굿,입주협의가능</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -5838,7 +6885,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43256614</t>
+          <t>43388036</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5868,7 +6915,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -5884,12 +6931,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -5899,7 +6946,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -5908,25 +6955,33 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O전세도이강O거실넓은뻥뷰,영상참고하세요</t>
+          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -5945,7 +7000,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43252795</t>
+          <t>43388023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5955,27 +7010,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -5996,7 +7051,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -6006,7 +7061,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -6015,11 +7070,7 @@
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>O</t>
@@ -6027,21 +7078,17 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
+          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -6060,7 +7107,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>43251918</t>
+          <t>43388001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6070,27 +7117,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -6111,7 +7158,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -6121,7 +7168,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -6135,12 +7182,12 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
@@ -6149,14 +7196,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -6175,7 +7222,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43251902</t>
+          <t>43423016</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6185,22 +7232,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -6226,7 +7273,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -6236,7 +7283,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6251,7 +7298,11 @@
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>O</t>
@@ -6260,14 +7311,14 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -6286,7 +7337,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>43210459</t>
+          <t>43423017</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6296,27 +7347,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -6337,7 +7388,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -6347,7 +7398,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -6356,16 +7407,8 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
@@ -6375,14 +7418,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O이강O빠른입주환영,현금전세,에어컨4,채광굿</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>45000</v>
+        <v>53000</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6401,7 +7444,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>43199433</t>
+          <t>43344149</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6411,12 +7454,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6431,7 +7474,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -6452,7 +7495,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -6462,7 +7505,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -6471,17 +7514,9 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>O</t>
@@ -6490,14 +7525,14 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
+          <t>O안전전세도이강O옵션가득한집,냉장고3,세탁기,인덕션등</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6516,7 +7551,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43164195</t>
+          <t>43355343</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6526,7 +7561,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>117동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6546,7 +7581,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -6567,7 +7602,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6577,7 +7612,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -6593,22 +7628,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
+          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -6627,7 +7658,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43124662</t>
+          <t>43355345</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6637,27 +7668,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -6678,7 +7709,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6688,7 +7719,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -6702,28 +7733,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
+          <t>O전세대출가능O상시집보여드려요,당일확인,중문,에어컨4</t>
         </is>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -6742,7 +7773,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43070764</t>
+          <t>43301888</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6752,27 +7783,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>121동</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -6793,7 +7824,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6803,7 +7834,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -6812,29 +7843,29 @@
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O전세대출가능O와이드주방,채광좋아요,조용하고따뜻한동</t>
+          <t>O안전전세도이강O현금전세,빠른입주환영,에어컨4</t>
         </is>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>55000</v>
+        <v>50000</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -6853,7 +7884,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>42952675</t>
+          <t>43256614</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6863,7 +7894,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6899,7 +7930,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -6914,7 +7945,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -6927,14 +7958,18 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>O조건맞춰찾아드립니다O전월세매물많은집</t>
+          <t>O전세도이강O거실넓은뻥뷰,영상참고하세요</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z16" t="n">
         <v>55000</v>
@@ -6956,7 +7991,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42852176</t>
+          <t>43251902</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6966,27 +8001,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -7007,7 +8042,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7017,7 +8052,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -7026,13 +8061,13 @@
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>O</t>
@@ -7041,14 +8076,14 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -7067,7 +8102,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>43210459</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7077,17 +8112,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>125동</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7097,7 +8132,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -7118,7 +8153,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7128,7 +8163,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -7137,33 +8172,33 @@
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
+          <t>O이강O빠른입주환영,현금전세,에어컨4,채광굿</t>
         </is>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>47000</v>
+        <v>45000</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -7182,7 +8217,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42558979</t>
+          <t>43164195</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7192,33 +8227,33 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>128동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -7233,7 +8268,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -7243,7 +8278,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -7253,28 +8288,28 @@
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>O71타입로얄동O채광굿,입주협의가능</t>
+          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
         </is>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -7293,7 +8328,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42490328</t>
+          <t>43070764</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7303,7 +8338,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7323,7 +8358,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -7344,7 +8379,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -7354,7 +8389,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -7363,33 +8398,29 @@
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
+          <t>O전세대출가능O와이드주방,채광좋아요,조용하고따뜻한동</t>
         </is>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -7408,7 +8439,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42441234</t>
+          <t>42852176</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7418,7 +8449,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7438,7 +8469,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -7469,7 +8500,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -7479,17 +8510,21 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
+          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -7513,7 +8548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7666,7 +8701,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43252135</t>
+          <t>43391132</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7676,7 +8711,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -7696,13 +8731,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -7717,17 +8752,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -7736,28 +8771,36 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
+          <t>O늦은입주OKO전입X,시에4,실링팬,중문,입주청소</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="AA2" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
@@ -7773,7 +8816,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43252123</t>
+          <t>43388011</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7834,7 +8877,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -7884,7 +8927,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43160256</t>
+          <t>43252135</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7894,33 +8937,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -7935,17 +8978,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -7955,35 +8998,27 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="AA4" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -7999,7 +9034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43070716</t>
+          <t>43160256</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8009,27 +9044,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>107동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -8050,17 +9085,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -8070,13 +9105,17 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>O</t>
@@ -8084,17 +9123,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O전입가능O입주협의,융무,채광좋은집</t>
+          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="AA5" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -8110,7 +9149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42952648</t>
+          <t>43070716</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8120,27 +9159,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>107동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -8161,17 +9200,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -8181,7 +9220,11 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
@@ -8191,17 +9234,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
+          <t>O전입가능O입주협의,융무,채광좋은집</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -8217,7 +9260,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42952559</t>
+          <t>42952648</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8227,17 +9270,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>123동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8247,7 +9290,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -8273,7 +9316,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -8287,17 +9330,9 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
@@ -8306,7 +9341,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -8316,6 +9351,121 @@
         <v>30000</v>
       </c>
       <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>42952559</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>매교역팰루시드</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>122동</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>101.34</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>71.89</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>월세</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>팰루시드이강부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA8" t="n">
         <v>110</v>
       </c>
     </row>
